--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_2_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_2_bus.xlsx
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9380319009554193</v>
+        <v>0.9380319009554191</v>
       </c>
       <c r="G2">
-        <v>-1.130199521952461</v>
+        <v>-1.130199521952451</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.291705603738297</v>
+        <v>0.2917056037382958</v>
       </c>
       <c r="G3">
-        <v>-29.17137735526047</v>
+        <v>-29.17137735526041</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -572,22 +572,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.28296261028849</v>
+        <v>4.282962610288493</v>
       </c>
       <c r="C4">
-        <v>148.3661769587497</v>
+        <v>148.3661769587498</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354134</v>
+        <v>0.627731916335411</v>
       </c>
       <c r="E4">
-        <v>2.898438697960062</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051343</v>
+        <v>77.77984578051345</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -808,16 +808,16 @@
         <v>1.031611214669993</v>
       </c>
       <c r="O3">
-        <v>0.291705603751294</v>
+        <v>0.2917056037512938</v>
       </c>
       <c r="P3">
-        <v>0.8906876332644386</v>
+        <v>0.8906876332644384</v>
       </c>
       <c r="Q3">
-        <v>7.091324389062551</v>
+        <v>7.091324389062541</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550798</v>
+        <v>-119.1713773550799</v>
       </c>
       <c r="S3">
         <v>171.7794727726615</v>
@@ -831,40 +831,40 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.709154423937068</v>
+        <v>3.709154423937074</v>
       </c>
       <c r="D4">
-        <v>3.709154423937068</v>
+        <v>3.709154423937074</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.82962610251915</v>
+        <v>42.82962610251921</v>
       </c>
       <c r="G4">
-        <v>42.82962610251915</v>
+        <v>42.82962610251921</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
-        <v>0.9526279648032085</v>
+        <v>0.9526279648032088</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>0.9526279648047558</v>
       </c>
       <c r="Q4">
-        <v>-1.250945197196156E-11</v>
+        <v>-1.251728646126886E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000115829797</v>
+        <v>0.9526279646110865</v>
       </c>
       <c r="O5">
-        <v>0.5500000122512996</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.100000023834279</v>
+        <v>0.9526279649968781</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999965509</v>
+        <v>1.148814058847454E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999965524</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.512112070702432E-13</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000115829797</v>
+        <v>0.9526279646110865</v>
       </c>
       <c r="O6">
-        <v>0.5500000122512996</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.100000023834279</v>
+        <v>0.9526279649968781</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999965509</v>
+        <v>1.148819995373461E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999965524</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.445337741185076E-13</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
   </sheetData>
@@ -1172,10 +1172,10 @@
         <v>1.109634423210917</v>
       </c>
       <c r="O3">
-        <v>0.7617779018710716</v>
+        <v>0.7617779018710719</v>
       </c>
       <c r="P3">
-        <v>0.9348070984869523</v>
+        <v>0.9348070984869525</v>
       </c>
       <c r="Q3">
         <v>19.43181595267037</v>
@@ -1195,34 +1195,34 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.763086650675506</v>
+        <v>1.763086650675505</v>
       </c>
       <c r="D4">
-        <v>1.763086650675506</v>
+        <v>1.763086650675505</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20.35837104744278</v>
+        <v>20.35837104744277</v>
       </c>
       <c r="G4">
-        <v>20.35837104744278</v>
+        <v>20.35837104744277</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
@@ -1231,7 +1231,7 @@
         <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.6233452632551811</v>
+        <v>0.6233452632551812</v>
       </c>
       <c r="P4">
         <v>0.9229411060011539</v>
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8641406623245683</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O5">
-        <v>0.6641535346773521</v>
+        <v>0.6233452631755219</v>
       </c>
       <c r="P5">
-        <v>1.100000023838383</v>
+        <v>0.9229411060761137</v>
       </c>
       <c r="Q5">
-        <v>-142.8672784161505</v>
+        <v>16.25665454976669</v>
       </c>
       <c r="R5">
-        <v>128.2389811397165</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S5">
-        <v>-1.185244348928629E-13</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8641406623245683</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O6">
-        <v>0.6641535346773522</v>
+        <v>0.6233452631755219</v>
       </c>
       <c r="P6">
-        <v>1.100000023838383</v>
+        <v>0.9229411060761136</v>
       </c>
       <c r="Q6">
-        <v>-142.8672784161505</v>
+        <v>16.25665454976669</v>
       </c>
       <c r="R6">
-        <v>128.2389811397165</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S6">
-        <v>-1.235325096066458E-13</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
   </sheetData>
@@ -1536,13 +1536,13 @@
         <v>1.109634423210917</v>
       </c>
       <c r="O3">
-        <v>0.7617779018710714</v>
+        <v>0.7617779018710719</v>
       </c>
       <c r="P3">
-        <v>0.9348070984869523</v>
+        <v>0.9348070984869525</v>
       </c>
       <c r="Q3">
-        <v>19.43181595267037</v>
+        <v>19.43181595267038</v>
       </c>
       <c r="R3">
         <v>-104.2565908665021</v>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.763086650675505</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="D4">
-        <v>1.763086650675505</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20.35837104744277</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="G4">
-        <v>20.35837104744277</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
         <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.6233452632551808</v>
+        <v>0.6233452632551815</v>
       </c>
       <c r="P4">
-        <v>0.922941106001154</v>
+        <v>0.9229411060011539</v>
       </c>
       <c r="Q4">
-        <v>16.25665454943075</v>
+        <v>16.25665454943076</v>
       </c>
       <c r="R4">
         <v>-104.9129785376843</v>
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8641406623180192</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O5">
-        <v>0.6641535346805325</v>
+        <v>0.6233452631717287</v>
       </c>
       <c r="P5">
-        <v>1.100000023838382</v>
+        <v>0.9229411060796834</v>
       </c>
       <c r="Q5">
-        <v>-142.867278415948</v>
+        <v>16.2566545497827</v>
       </c>
       <c r="R5">
-        <v>128.2389811402763</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S5">
-        <v>-1.185244348928629E-13</v>
+        <v>160.954389831599</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8641406623180192</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O6">
-        <v>0.6641535346805324</v>
+        <v>0.6233452631717288</v>
       </c>
       <c r="P6">
-        <v>1.100000023838382</v>
+        <v>0.9229411060796834</v>
       </c>
       <c r="Q6">
-        <v>-142.867278415948</v>
+        <v>16.25665454978271</v>
       </c>
       <c r="R6">
-        <v>128.2389811402763</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S6">
-        <v>-1.1351636017908E-13</v>
+        <v>160.954389831599</v>
       </c>
     </row>
   </sheetData>
@@ -1844,7 +1844,7 @@
         <v>0.850004952541402</v>
       </c>
       <c r="P2">
-        <v>0.9468598309457217</v>
+        <v>0.9468598309457219</v>
       </c>
       <c r="Q2">
         <v>25.60992326808852</v>
@@ -1897,22 +1897,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401370793</v>
+        <v>0.9900703401370795</v>
       </c>
       <c r="O3">
-        <v>0.3617201835030112</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
-        <v>0.764971546641112</v>
+        <v>0.7649715466411122</v>
       </c>
       <c r="Q3">
-        <v>8.150888684274483</v>
+        <v>8.150888684274459</v>
       </c>
       <c r="R3">
         <v>-129.0915432241893</v>
       </c>
       <c r="S3">
-        <v>169.4262793833646</v>
+        <v>169.4262793833645</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1923,55 +1923,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825515526</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="D4">
-        <v>3.119085825515526</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.0161008197387</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="G4">
-        <v>36.0161008197387</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8660254037880055</v>
+        <v>0.8660254037880057</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037883346</v>
+        <v>0.866025403788335</v>
       </c>
       <c r="Q4">
-        <v>1.723648388515596E-10</v>
+        <v>1.723276128173253E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999998195</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999996985027</v>
+        <v>0.8660254036128882</v>
       </c>
       <c r="O5">
-        <v>0.5000000003057972</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634528</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999959872</v>
+        <v>1.336744061854895E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>8.116419928662335E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999996985026</v>
+        <v>0.8660254036128882</v>
       </c>
       <c r="O6">
-        <v>0.5000000003057973</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634528</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999959872</v>
+        <v>1.33673563290738E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>8.116419928662335E-13</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2208,7 @@
         <v>0.850004952541402</v>
       </c>
       <c r="P2">
-        <v>0.9468598309457217</v>
+        <v>0.9468598309457219</v>
       </c>
       <c r="Q2">
         <v>25.60992326808852</v>
@@ -2261,22 +2261,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401370793</v>
+        <v>0.9900703401370795</v>
       </c>
       <c r="O3">
-        <v>0.3617201835030112</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
-        <v>0.764971546641112</v>
+        <v>0.7649715466411122</v>
       </c>
       <c r="Q3">
-        <v>8.150888684274483</v>
+        <v>8.150888684274459</v>
       </c>
       <c r="R3">
         <v>-129.0915432241893</v>
       </c>
       <c r="S3">
-        <v>169.4262793833646</v>
+        <v>169.4262793833645</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2287,55 +2287,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825515526</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="D4">
-        <v>3.119085825515526</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.0161008197387</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="G4">
-        <v>36.0161008197387</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8660254037880055</v>
+        <v>0.8660254037880057</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037883346</v>
+        <v>0.866025403788335</v>
       </c>
       <c r="Q4">
-        <v>1.723648388515596E-10</v>
+        <v>1.723276128173253E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999998195</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999996985027</v>
+        <v>0.8660254036128882</v>
       </c>
       <c r="O5">
-        <v>0.5000000003057972</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634528</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999959872</v>
+        <v>1.336744061854895E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>8.116419928662335E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999996985026</v>
+        <v>0.8660254036128882</v>
       </c>
       <c r="O6">
-        <v>0.5000000003057973</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634528</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999959872</v>
+        <v>1.33673563290738E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>8.116419928662335E-13</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
   </sheetData>
@@ -2628,13 +2628,13 @@
         <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959566594</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
         <v>0.8449321159941328</v>
       </c>
       <c r="Q3">
-        <v>19.61176266474869</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
         <v>-105.2709110729077</v>
@@ -2666,34 +2666,34 @@
         <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119604</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.5367995610775462</v>
+        <v>0.5367995610775461</v>
       </c>
       <c r="P4">
-        <v>0.8529812840863317</v>
+        <v>0.8529812840863319</v>
       </c>
       <c r="Q4">
-        <v>15.93288697155596</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
         <v>-101.7238138495563</v>
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7487167004860203</v>
+        <v>0.957339967427279</v>
       </c>
       <c r="O5">
-        <v>0.6096342801113653</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P5">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638803</v>
       </c>
       <c r="Q5">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R5">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>4.957994074073165E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7487167004860203</v>
+        <v>0.957339967427279</v>
       </c>
       <c r="O6">
-        <v>0.6096342801113653</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638803</v>
       </c>
       <c r="Q6">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>4.407105843620591E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -2992,13 +2992,13 @@
         <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959566594</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
         <v>0.8449321159941328</v>
       </c>
       <c r="Q3">
-        <v>19.61176266474869</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
         <v>-105.2709110729077</v>
@@ -3030,34 +3030,34 @@
         <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119604</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.5367995610775462</v>
+        <v>0.5367995610775461</v>
       </c>
       <c r="P4">
-        <v>0.8529812840863317</v>
+        <v>0.8529812840863319</v>
       </c>
       <c r="Q4">
-        <v>15.93288697155596</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
         <v>-101.7238138495563</v>
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7487167004860203</v>
+        <v>0.957339967427279</v>
       </c>
       <c r="O5">
-        <v>0.6096342801113653</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P5">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638803</v>
       </c>
       <c r="Q5">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R5">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>4.957994074073165E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7487167004860203</v>
+        <v>0.957339967427279</v>
       </c>
       <c r="O6">
-        <v>0.6096342801113653</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638803</v>
       </c>
       <c r="Q6">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>4.407105843620591E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -3303,7 +3303,7 @@
         <v>1.100000023846546</v>
       </c>
       <c r="P2">
-        <v>1.052974491478999</v>
+        <v>1.052974491478998</v>
       </c>
       <c r="Q2">
         <v>30.27740992635148</v>
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467346737965</v>
+        <v>0.6205467346737962</v>
       </c>
       <c r="O3">
         <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.9549975894344677</v>
+        <v>0.9549975894344676</v>
       </c>
       <c r="Q3">
-        <v>30.02212424388603</v>
+        <v>30.02212424388602</v>
       </c>
       <c r="R3">
         <v>-89.99999999999648</v>
@@ -3385,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.149403058432902</v>
+        <v>4.1494030584329</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.91317945524985</v>
+        <v>47.91317945524982</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3403,43 +3403,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
       </c>
       <c r="N4">
-        <v>0.5038029474387167</v>
+        <v>0.5038029474387162</v>
       </c>
       <c r="O4">
         <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527588186367</v>
+        <v>0.8521527588186363</v>
       </c>
       <c r="Q4">
         <v>41.72313523393699</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999623</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
         <v>116.1844690692805</v>
       </c>
       <c r="T4">
-        <v>4.149403058432902</v>
+        <v>4.149403058432899</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8566350060579376</v>
+        <v>0.5038029475324125</v>
       </c>
       <c r="O5">
-        <v>1.098257914917705</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P5">
-        <v>0.4999878050007198</v>
+        <v>0.8521527586165758</v>
       </c>
       <c r="Q5">
-        <v>-104.6805795097902</v>
+        <v>41.72313525482286</v>
       </c>
       <c r="R5">
-        <v>101.400975717282</v>
+        <v>-89.99999999999567</v>
       </c>
       <c r="S5">
-        <v>-29.72566761418698</v>
+        <v>116.1844690720437</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8566350060579375</v>
+        <v>0.5038029475324124</v>
       </c>
       <c r="O6">
-        <v>1.098257914917705</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P6">
-        <v>0.4999878050007197</v>
+        <v>0.8521527586165759</v>
       </c>
       <c r="Q6">
-        <v>-104.6805795097902</v>
+        <v>41.72313525482285</v>
       </c>
       <c r="R6">
-        <v>101.400975717282</v>
+        <v>-89.99999999999567</v>
       </c>
       <c r="S6">
-        <v>-29.72566761418699</v>
+        <v>116.1844690720437</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3691,7 +3691,7 @@
         <v>30.27740992635148</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
         <v>145.833649147256</v>
@@ -3741,19 +3741,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467346737964</v>
+        <v>0.6205467346737963</v>
       </c>
       <c r="O3">
         <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.954997589434468</v>
+        <v>0.9549975894344678</v>
       </c>
       <c r="Q3">
-        <v>30.02212424388598</v>
+        <v>30.02212424388602</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999646</v>
       </c>
       <c r="S3">
         <v>124.2363583956003</v>
@@ -3767,7 +3767,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.149403058432898</v>
+        <v>4.149403058432899</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.91317945524981</v>
+        <v>47.91317945524982</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3785,37 +3785,37 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
-        <v>0.5038029474387163</v>
+        <v>0.5038029474387166</v>
       </c>
       <c r="O4">
         <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527588186371</v>
+        <v>0.8521527588186369</v>
       </c>
       <c r="Q4">
-        <v>41.72313523393694</v>
+        <v>41.72313523393698</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999623</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
         <v>116.1844690692805</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8566350060628778</v>
+        <v>0.5038029475368762</v>
       </c>
       <c r="O5">
-        <v>1.098257914912045</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P5">
-        <v>0.4999878049927863</v>
+        <v>0.8521527586069548</v>
       </c>
       <c r="Q5">
-        <v>-104.6805795096043</v>
+        <v>41.72313525581742</v>
       </c>
       <c r="R5">
-        <v>101.400975717265</v>
+        <v>-89.99999999999567</v>
       </c>
       <c r="S5">
-        <v>-29.72566761325894</v>
+        <v>116.1844690721753</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8566350060628778</v>
+        <v>0.5038029475368763</v>
       </c>
       <c r="O6">
-        <v>1.098257914912045</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P6">
-        <v>0.4999878049927863</v>
+        <v>0.8521527586069548</v>
       </c>
       <c r="Q6">
-        <v>-104.6805795096043</v>
+        <v>41.72313525581741</v>
       </c>
       <c r="R6">
-        <v>101.400975717265</v>
+        <v>-89.99999999999567</v>
       </c>
       <c r="S6">
-        <v>-29.72566761325893</v>
+        <v>116.1844690721753</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4123,13 +4123,13 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9563222180694877</v>
+        <v>0.9563222180694876</v>
       </c>
       <c r="O3">
-        <v>1.100000023844968</v>
+        <v>1.100000023844967</v>
       </c>
       <c r="P3">
-        <v>1.055630524129933</v>
+        <v>1.055630524129932</v>
       </c>
       <c r="Q3">
         <v>28.69534087753231</v>
@@ -4149,7 +4149,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.259771140028916</v>
+        <v>1.259771140028915</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4167,28 +4167,28 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
       </c>
       <c r="N4">
-        <v>0.9132295418291422</v>
+        <v>0.9132295418291418</v>
       </c>
       <c r="O4">
-        <v>1.100000023844968</v>
+        <v>1.100000023844967</v>
       </c>
       <c r="P4">
         <v>1.016646408614733</v>
@@ -4203,7 +4203,7 @@
         <v>140.9330581974619</v>
       </c>
       <c r="T4">
-        <v>1.259771140028916</v>
+        <v>1.259771140028915</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.009027019302548</v>
+        <v>0.9132295418366294</v>
       </c>
       <c r="O5">
-        <v>1.103502265351497</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P5">
-        <v>0.9174450355526041</v>
+        <v>1.016646408559263</v>
       </c>
       <c r="Q5">
-        <v>-116.8493087016271</v>
+        <v>30.19334881017324</v>
       </c>
       <c r="R5">
-        <v>114.3920679454526</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S5">
-        <v>-6.556290856891474</v>
+        <v>140.9330581990972</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.009027019302548</v>
+        <v>0.9132295418366294</v>
       </c>
       <c r="O6">
-        <v>1.103502265351497</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P6">
-        <v>0.9174450355526041</v>
+        <v>1.016646408559263</v>
       </c>
       <c r="Q6">
-        <v>-116.8493087016271</v>
+        <v>30.19334881017324</v>
       </c>
       <c r="R6">
-        <v>114.3920679454526</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S6">
-        <v>-6.556290856891476</v>
+        <v>140.9330581990972</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9380319009554188</v>
+        <v>0.9380319009554193</v>
       </c>
       <c r="G2">
-        <v>-1.130199521952468</v>
+        <v>-1.130199521952445</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.2917056037382955</v>
+        <v>0.2917056037382966</v>
       </c>
       <c r="G3">
-        <v>-29.1713773552608</v>
+        <v>-29.17137735526021</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4414,22 +4414,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.282962610288492</v>
+        <v>4.282962610288489</v>
       </c>
       <c r="C4">
-        <v>148.3661769587498</v>
+        <v>148.3661769587497</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354138</v>
+        <v>0.6277319163354118</v>
       </c>
       <c r="E4">
-        <v>2.898438697960061</v>
+        <v>2.898438697960063</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051341</v>
+        <v>77.77984578051345</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9563222180694876</v>
+        <v>0.9563222180694877</v>
       </c>
       <c r="O3">
         <v>1.100000023844968</v>
@@ -4662,7 +4662,7 @@
         <v>1.055630524129933</v>
       </c>
       <c r="Q3">
-        <v>28.6953408775323</v>
+        <v>28.69534087753229</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
@@ -4679,7 +4679,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.259771140028915</v>
+        <v>1.259771140028916</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4697,22 +4697,22 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
         <v>0.9132295418291418</v>
@@ -4733,7 +4733,7 @@
         <v>140.9330581974619</v>
       </c>
       <c r="T4">
-        <v>1.259771140028915</v>
+        <v>1.259771140028916</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.00902701930365</v>
+        <v>0.9132295418369862</v>
       </c>
       <c r="O5">
-        <v>1.103502265349776</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P5">
-        <v>0.9174450355508896</v>
+        <v>1.016646408556622</v>
       </c>
       <c r="Q5">
-        <v>-116.8493087015521</v>
+        <v>30.19334881035892</v>
       </c>
       <c r="R5">
-        <v>114.3920679454542</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S5">
-        <v>-6.556290856705083</v>
+        <v>140.9330581991751</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.00902701930365</v>
+        <v>0.9132295418369865</v>
       </c>
       <c r="O6">
-        <v>1.103502265349776</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P6">
-        <v>0.9174450355508896</v>
+        <v>1.016646408556622</v>
       </c>
       <c r="Q6">
-        <v>-116.8493087015521</v>
+        <v>30.19334881035892</v>
       </c>
       <c r="R6">
-        <v>114.3920679454542</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S6">
-        <v>-6.556290856705079</v>
+        <v>140.9330581991751</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5035,16 +5035,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6800187783876563</v>
+        <v>0.6800187783876562</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P3">
-        <v>0.9802656726501164</v>
+        <v>0.9802656726501163</v>
       </c>
       <c r="Q3">
-        <v>21.6381347987348</v>
+        <v>21.63813479873481</v>
       </c>
       <c r="R3">
         <v>-89.99999999999662</v>
@@ -5061,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014555890701</v>
+        <v>2.826014555890703</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5070,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.63200529154594</v>
+        <v>32.63200529154597</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5079,34 +5079,34 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.5470567493003653</v>
+        <v>0.5470567493003652</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P4">
-        <v>0.8611554265665965</v>
+        <v>0.8611554265665962</v>
       </c>
       <c r="Q4">
-        <v>30.64462611762081</v>
+        <v>30.64462611762084</v>
       </c>
       <c r="R4">
         <v>-89.99999999999622</v>
@@ -5115,7 +5115,7 @@
         <v>123.1301085477829</v>
       </c>
       <c r="T4">
-        <v>2.8260145558907</v>
+        <v>2.826014555890703</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202071</v>
       </c>
       <c r="O5">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P5">
-        <v>0.6004774519284559</v>
+        <v>0.8611554264093789</v>
       </c>
       <c r="Q5">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419062</v>
       </c>
       <c r="R5">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S5">
-        <v>-25.16850627980605</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O6">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P6">
-        <v>0.6004774519284559</v>
+        <v>0.861155426409379</v>
       </c>
       <c r="Q6">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419061</v>
       </c>
       <c r="R6">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S6">
-        <v>-25.16850627980605</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5417,16 +5417,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6800187783876563</v>
+        <v>0.6800187783876562</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P3">
-        <v>0.9802656726501164</v>
+        <v>0.9802656726501163</v>
       </c>
       <c r="Q3">
-        <v>21.6381347987348</v>
+        <v>21.63813479873481</v>
       </c>
       <c r="R3">
         <v>-89.99999999999662</v>
@@ -5443,7 +5443,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014555890701</v>
+        <v>2.826014555890703</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.63200529154594</v>
+        <v>32.63200529154597</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5461,34 +5461,34 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.5470567493003653</v>
+        <v>0.5470567493003652</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P4">
-        <v>0.8611554265665965</v>
+        <v>0.8611554265665962</v>
       </c>
       <c r="Q4">
-        <v>30.64462611762081</v>
+        <v>30.64462611762084</v>
       </c>
       <c r="R4">
         <v>-89.99999999999622</v>
@@ -5497,7 +5497,7 @@
         <v>123.1301085477829</v>
       </c>
       <c r="T4">
-        <v>2.8260145558907</v>
+        <v>2.826014555890703</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202071</v>
       </c>
       <c r="O5">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P5">
-        <v>0.6004774519284559</v>
+        <v>0.8611554264093789</v>
       </c>
       <c r="Q5">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419062</v>
       </c>
       <c r="R5">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S5">
-        <v>-25.16850627980605</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O6">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P6">
-        <v>0.6004774519284559</v>
+        <v>0.861155426409379</v>
       </c>
       <c r="Q6">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419061</v>
       </c>
       <c r="R6">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S6">
-        <v>-25.16850627980605</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5746,7 +5746,7 @@
         <v>0.991853010532729</v>
       </c>
       <c r="Q2">
-        <v>29.71071470941858</v>
+        <v>29.71071470941859</v>
       </c>
       <c r="R2">
         <v>-89.99999999999636</v>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8789265977783917</v>
+        <v>0.8789265977783918</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
-        <v>0.9728049023577379</v>
+        <v>0.9728049023577376</v>
       </c>
       <c r="Q3">
-        <v>28.03324723559998</v>
+        <v>28.03324723559999</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
@@ -5843,22 +5843,22 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
         <v>0.834378493082676</v>
@@ -5867,10 +5867,10 @@
         <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367072738</v>
+        <v>0.9184277367072736</v>
       </c>
       <c r="Q4">
-        <v>30.72819116678024</v>
+        <v>30.72819116678026</v>
       </c>
       <c r="R4">
         <v>-89.99999999999631</v>
@@ -5879,7 +5879,7 @@
         <v>141.3462823800049</v>
       </c>
       <c r="T4">
-        <v>1.035710406550306</v>
+        <v>1.035710406550307</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O5">
-        <v>0.9984707549023012</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P5">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570414</v>
       </c>
       <c r="Q5">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R5">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S5">
-        <v>-5.863816409929022</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O6">
-        <v>0.9984707549023012</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P6">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570415</v>
       </c>
       <c r="Q6">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R6">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S6">
-        <v>-5.863816409929023</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6128,7 +6128,7 @@
         <v>0.991853010532729</v>
       </c>
       <c r="Q2">
-        <v>29.71071470941858</v>
+        <v>29.71071470941859</v>
       </c>
       <c r="R2">
         <v>-89.99999999999636</v>
@@ -6181,16 +6181,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8789265977783917</v>
+        <v>0.8789265977783918</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
-        <v>0.9728049023577379</v>
+        <v>0.9728049023577376</v>
       </c>
       <c r="Q3">
-        <v>28.03324723559998</v>
+        <v>28.03324723559999</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
@@ -6225,22 +6225,22 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
         <v>0.834378493082676</v>
@@ -6249,10 +6249,10 @@
         <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367072738</v>
+        <v>0.9184277367072736</v>
       </c>
       <c r="Q4">
-        <v>30.72819116678024</v>
+        <v>30.72819116678026</v>
       </c>
       <c r="R4">
         <v>-89.99999999999631</v>
@@ -6261,7 +6261,7 @@
         <v>141.3462823800049</v>
       </c>
       <c r="T4">
-        <v>1.035710406550306</v>
+        <v>1.035710406550307</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O5">
-        <v>0.9984707549023012</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P5">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570414</v>
       </c>
       <c r="Q5">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R5">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S5">
-        <v>-5.863816409929022</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O6">
-        <v>0.9984707549023012</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P6">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570415</v>
       </c>
       <c r="Q6">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R6">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S6">
-        <v>-5.863816409929023</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6566,13 +6566,13 @@
         <v>0.8815655946738199</v>
       </c>
       <c r="O3">
-        <v>0.2917056037516222</v>
+        <v>0.2917056037516224</v>
       </c>
       <c r="P3">
         <v>0.7906583687018802</v>
       </c>
       <c r="Q3">
-        <v>-1.71845846349944</v>
+        <v>-1.718458463499419</v>
       </c>
       <c r="R3">
         <v>-119.1713773545954</v>
@@ -6592,34 +6592,34 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.026925726064773</v>
+        <v>5.026925726064771</v>
       </c>
       <c r="D4">
-        <v>2.971978874802877</v>
+        <v>2.971978874802881</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593842279504</v>
+        <v>58.04593842279502</v>
       </c>
       <c r="G4">
-        <v>34.31745606786644</v>
+        <v>34.31745606786649</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
@@ -6631,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7575177917593717</v>
+        <v>0.7575177917593718</v>
       </c>
       <c r="Q4">
-        <v>-12.52501517673263</v>
+        <v>-12.52501517673261</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -6643,7 +6643,7 @@
         <v>167.4749848232924</v>
       </c>
       <c r="T4">
-        <v>3.629597114345206</v>
+        <v>3.629597114345199</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4373531006292012</v>
+        <v>0.7575177915084544</v>
       </c>
       <c r="O5">
-        <v>0.4373531012715687</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8747062019007699</v>
+        <v>0.7575177918792887</v>
       </c>
       <c r="Q5">
-        <v>167.4749848231527</v>
+        <v>-12.52501517350586</v>
       </c>
       <c r="R5">
-        <v>167.4749848331493</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-12.52501517184175</v>
+        <v>167.4749848298125</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4373531006292011</v>
+        <v>0.7575177915084544</v>
       </c>
       <c r="O6">
-        <v>0.4373531012715688</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8747062019007699</v>
+        <v>0.7575177918792886</v>
       </c>
       <c r="Q6">
-        <v>167.4749848231527</v>
+        <v>-12.52501517350586</v>
       </c>
       <c r="R6">
-        <v>167.4749848331493</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-12.52501517184175</v>
+        <v>167.4749848298125</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6895,7 +6895,7 @@
         <v>25.29952259328411</v>
       </c>
       <c r="R2">
-        <v>-91.13019952198896</v>
+        <v>-91.13019952198897</v>
       </c>
       <c r="S2">
         <v>151.4964745421679</v>
@@ -6948,13 +6948,13 @@
         <v>0.8815655946738199</v>
       </c>
       <c r="O3">
-        <v>0.291705603751622</v>
+        <v>0.2917056037516218</v>
       </c>
       <c r="P3">
         <v>0.7906583687018803</v>
       </c>
       <c r="Q3">
-        <v>-1.718458463499423</v>
+        <v>-1.718458463499441</v>
       </c>
       <c r="R3">
         <v>-119.1713773545954</v>
@@ -6974,37 +6974,37 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.02692572606477</v>
+        <v>5.026925726064778</v>
       </c>
       <c r="D4">
-        <v>2.971978874802877</v>
+        <v>2.971978874802883</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593842279501</v>
+        <v>58.0459384227951</v>
       </c>
       <c r="G4">
-        <v>34.31745606786644</v>
+        <v>34.31745606786651</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
         <v>0.7575177917545732</v>
@@ -7016,7 +7016,7 @@
         <v>0.7575177917593718</v>
       </c>
       <c r="Q4">
-        <v>-12.52501517673262</v>
+        <v>-12.52501517673264</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>167.4749848232924</v>
       </c>
       <c r="T4">
-        <v>3.629597114345201</v>
+        <v>3.629597114345206</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4373531006123701</v>
+        <v>0.7575177914967339</v>
       </c>
       <c r="O5">
-        <v>0.4373531012849298</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8747062018972999</v>
+        <v>0.7575177918849989</v>
       </c>
       <c r="Q5">
-        <v>167.4749848231493</v>
+        <v>-12.52501517335231</v>
       </c>
       <c r="R5">
-        <v>167.4749848336167</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-12.52501517160969</v>
+        <v>167.474984830123</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4373531006123701</v>
+        <v>0.7575177914967336</v>
       </c>
       <c r="O6">
-        <v>0.4373531012849298</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8747062018972999</v>
+        <v>0.7575177918849989</v>
       </c>
       <c r="Q6">
-        <v>167.4749848231493</v>
+        <v>-12.52501517335231</v>
       </c>
       <c r="R6">
-        <v>167.4749848336167</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-12.5250151716097</v>
+        <v>167.474984830123</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7330,13 +7330,13 @@
         <v>1.049401079162727</v>
       </c>
       <c r="O3">
-        <v>0.8910570420399738</v>
+        <v>0.8910570420399742</v>
       </c>
       <c r="P3">
-        <v>0.9642317969850343</v>
+        <v>0.9642317969850347</v>
       </c>
       <c r="Q3">
-        <v>21.91294083447449</v>
+        <v>21.9129408344745</v>
       </c>
       <c r="R3">
         <v>-99.16867920487518</v>
@@ -7359,46 +7359,46 @@
         <v>1.382520063921417</v>
       </c>
       <c r="D4">
-        <v>1.176705138709485</v>
+        <v>1.176705138709486</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.96396662130178</v>
+        <v>15.96396662130177</v>
       </c>
       <c r="G4">
-        <v>13.58742057181474</v>
+        <v>13.58742057181475</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
       </c>
       <c r="N4">
-        <v>1.006459707631937</v>
+        <v>1.006459707631938</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380068</v>
+        <v>0.802015620938007</v>
       </c>
       <c r="P4">
-        <v>0.9269140407833438</v>
+        <v>0.9269140407833439</v>
       </c>
       <c r="Q4">
-        <v>20.05417835824807</v>
+        <v>20.05417835824808</v>
       </c>
       <c r="R4">
         <v>-99.52967390014048</v>
@@ -7407,7 +7407,7 @@
         <v>151.250781897275</v>
       </c>
       <c r="T4">
-        <v>1.202564331496538</v>
+        <v>1.202564331496539</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9042880734209771</v>
+        <v>1.006459707571176</v>
       </c>
       <c r="O5">
-        <v>0.8148284578940896</v>
+        <v>0.8020156208867663</v>
       </c>
       <c r="P5">
-        <v>1.01669931770016</v>
+        <v>0.9269140407971426</v>
       </c>
       <c r="Q5">
-        <v>-133.5033356425525</v>
+        <v>20.05417836007251</v>
       </c>
       <c r="R5">
-        <v>118.7983947242826</v>
+        <v>-99.52967389296813</v>
       </c>
       <c r="S5">
-        <v>-3.278220185527784</v>
+        <v>151.2507819007874</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9042880734209771</v>
+        <v>1.006459707571176</v>
       </c>
       <c r="O6">
-        <v>0.8148284578940896</v>
+        <v>0.8020156208867663</v>
       </c>
       <c r="P6">
-        <v>1.01669931770016</v>
+        <v>0.9269140407971426</v>
       </c>
       <c r="Q6">
-        <v>-133.5033356425525</v>
+        <v>20.05417836007251</v>
       </c>
       <c r="R6">
-        <v>118.7983947242826</v>
+        <v>-99.52967389296813</v>
       </c>
       <c r="S6">
-        <v>-3.278220185527784</v>
+        <v>151.2507819007874</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7712,13 +7712,13 @@
         <v>1.049401079162727</v>
       </c>
       <c r="O3">
-        <v>0.8910570420399738</v>
+        <v>0.8910570420399743</v>
       </c>
       <c r="P3">
         <v>0.9642317969850345</v>
       </c>
       <c r="Q3">
-        <v>21.9129408344745</v>
+        <v>21.91294083447451</v>
       </c>
       <c r="R3">
         <v>-99.16867920487518</v>
@@ -7741,46 +7741,46 @@
         <v>1.382520063921417</v>
       </c>
       <c r="D4">
-        <v>1.176705138709485</v>
+        <v>1.176705138709486</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.96396662130177</v>
+        <v>15.96396662130178</v>
       </c>
       <c r="G4">
-        <v>13.58742057181474</v>
+        <v>13.58742057181475</v>
       </c>
       <c r="H4">
-        <v>3.698069333823731</v>
+        <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753644</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162212</v>
+        <v>0.6277319163162199</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639754</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959987</v>
       </c>
       <c r="N4">
-        <v>1.006459707631937</v>
+        <v>1.006459707631938</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380067</v>
+        <v>0.8020156209380072</v>
       </c>
       <c r="P4">
         <v>0.9269140407833439</v>
       </c>
       <c r="Q4">
-        <v>20.05417835824807</v>
+        <v>20.05417835824809</v>
       </c>
       <c r="R4">
         <v>-99.52967390014047</v>
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9042880734171623</v>
+        <v>1.006459707568282</v>
       </c>
       <c r="O5">
-        <v>0.8148284578941781</v>
+        <v>0.8020156208843262</v>
       </c>
       <c r="P5">
-        <v>1.016699317699292</v>
+        <v>0.9269140407977997</v>
       </c>
       <c r="Q5">
-        <v>-133.5033356423602</v>
+        <v>20.05417836015939</v>
       </c>
       <c r="R5">
-        <v>118.7983947246034</v>
+        <v>-99.52967389262658</v>
       </c>
       <c r="S5">
-        <v>-3.278220185449197</v>
+        <v>151.2507819009546</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9042880734171623</v>
+        <v>1.006459707568282</v>
       </c>
       <c r="O6">
-        <v>0.8148284578941781</v>
+        <v>0.8020156208843263</v>
       </c>
       <c r="P6">
-        <v>1.016699317699292</v>
+        <v>0.9269140407977997</v>
       </c>
       <c r="Q6">
-        <v>-133.5033356423602</v>
+        <v>20.0541783601594</v>
       </c>
       <c r="R6">
-        <v>118.7983947246034</v>
+        <v>-99.52967389262658</v>
       </c>
       <c r="S6">
-        <v>-3.278220185449196</v>
+        <v>151.2507819009546</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8029,16 +8029,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9610470638492223</v>
+        <v>0.9610470638492222</v>
       </c>
       <c r="O2">
         <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649312407</v>
+        <v>0.9457332649312409</v>
       </c>
       <c r="Q2">
-        <v>24.73981956262405</v>
+        <v>24.73981956262404</v>
       </c>
       <c r="R2">
         <v>-92.65381631332205</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954518986</v>
+        <v>0.9239910954518991</v>
       </c>
       <c r="O3">
         <v>0.3617201835032895</v>
       </c>
       <c r="P3">
-        <v>0.7395562363454171</v>
+        <v>0.7395562363454176</v>
       </c>
       <c r="Q3">
-        <v>1.807833433806283</v>
+        <v>1.807833433806252</v>
       </c>
       <c r="R3">
         <v>-129.0915432241741</v>
       </c>
       <c r="S3">
-        <v>160.1110426204012</v>
+        <v>160.1110426204011</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256815303</v>
+        <v>3.921619256815305</v>
       </c>
       <c r="D4">
         <v>2.491243992016263</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295867163072</v>
+        <v>45.28295867163073</v>
       </c>
       <c r="G4">
         <v>28.76640778815255</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.7592484163866734</v>
+        <v>0.7592484163866735</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7592484163873851</v>
+        <v>0.7592484163873853</v>
       </c>
       <c r="Q4">
-        <v>-8.930089733930945</v>
+        <v>-8.930089733930989</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>171.0699102656345</v>
       </c>
       <c r="T4">
-        <v>2.063008215864349</v>
+        <v>2.063008215864351</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4383522772526091</v>
+        <v>0.7592484161672617</v>
       </c>
       <c r="O5">
-        <v>0.4383522778626269</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.876704555115236</v>
+        <v>0.7592484165194174</v>
       </c>
       <c r="Q5">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767257</v>
       </c>
       <c r="R5">
-        <v>171.0699102703369</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-8.930089731241013</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4383522772526093</v>
+        <v>0.7592484161672617</v>
       </c>
       <c r="O6">
-        <v>0.4383522778626268</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.876704555115236</v>
+        <v>0.7592484165194174</v>
       </c>
       <c r="Q6">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767266</v>
       </c>
       <c r="R6">
-        <v>171.0699102703369</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-8.930089731241019</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>1.056966443490338</v>
       </c>
       <c r="G2">
-        <v>-1.342925561278415</v>
+        <v>-1.342925561278414</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8374,7 +8374,7 @@
         <v>0.8910570420386134</v>
       </c>
       <c r="G3">
-        <v>-9.168679204911154</v>
+        <v>-9.168679204911147</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8382,22 +8382,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.309686024696609</v>
+        <v>1.30968602469661</v>
       </c>
       <c r="C4">
-        <v>45.36885473474868</v>
+        <v>45.36885473474869</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354134</v>
+        <v>0.627731916335411</v>
       </c>
       <c r="E4">
-        <v>2.898438697960062</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
-        <v>0.8020156209364414</v>
+        <v>0.8020156209364413</v>
       </c>
       <c r="G4">
-        <v>45.00000000014393</v>
+        <v>45.00000000014394</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8020156208852063</v>
+        <v>0.8020156208851952</v>
       </c>
       <c r="G5">
-        <v>-159.5296738930015</v>
+        <v>-9.529673893007812</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8020156208852063</v>
+        <v>0.8020156208851952</v>
       </c>
       <c r="G6">
-        <v>-159.5296738930015</v>
+        <v>-9.529673893007812</v>
       </c>
     </row>
   </sheetData>
@@ -8559,16 +8559,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9610470638492223</v>
+        <v>0.9610470638492222</v>
       </c>
       <c r="O2">
         <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649312407</v>
+        <v>0.9457332649312409</v>
       </c>
       <c r="Q2">
-        <v>24.73981956262405</v>
+        <v>24.73981956262404</v>
       </c>
       <c r="R2">
         <v>-92.65381631332205</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954518986</v>
+        <v>0.9239910954518991</v>
       </c>
       <c r="O3">
         <v>0.3617201835032895</v>
       </c>
       <c r="P3">
-        <v>0.7395562363454171</v>
+        <v>0.7395562363454176</v>
       </c>
       <c r="Q3">
-        <v>1.807833433806283</v>
+        <v>1.807833433806252</v>
       </c>
       <c r="R3">
         <v>-129.0915432241741</v>
       </c>
       <c r="S3">
-        <v>160.1110426204012</v>
+        <v>160.1110426204011</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256815303</v>
+        <v>3.921619256815305</v>
       </c>
       <c r="D4">
         <v>2.491243992016263</v>
@@ -8659,40 +8659,40 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295867163072</v>
+        <v>45.28295867163073</v>
       </c>
       <c r="G4">
         <v>28.76640778815255</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.7592484163866734</v>
+        <v>0.7592484163866735</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7592484163873851</v>
+        <v>0.7592484163873853</v>
       </c>
       <c r="Q4">
-        <v>-8.930089733930945</v>
+        <v>-8.930089733930989</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8701,7 +8701,7 @@
         <v>171.0699102656345</v>
       </c>
       <c r="T4">
-        <v>2.063008215864349</v>
+        <v>2.063008215864351</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4383522772526091</v>
+        <v>0.7592484161672617</v>
       </c>
       <c r="O5">
-        <v>0.4383522778626269</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.876704555115236</v>
+        <v>0.7592484165194174</v>
       </c>
       <c r="Q5">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767257</v>
       </c>
       <c r="R5">
-        <v>171.0699102703369</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-8.930089731241013</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4383522772526093</v>
+        <v>0.7592484161672617</v>
       </c>
       <c r="O6">
-        <v>0.4383522778626268</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.876704555115236</v>
+        <v>0.7592484165194174</v>
       </c>
       <c r="Q6">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767266</v>
       </c>
       <c r="R6">
-        <v>171.0699102703369</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-8.930089731241019</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9003,16 +9003,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209809371</v>
+        <v>0.9677452209809372</v>
       </c>
       <c r="O3">
-        <v>0.8139299031202699</v>
+        <v>0.8139299031202697</v>
       </c>
       <c r="P3">
-        <v>0.883172455503468</v>
+        <v>0.8831724555034682</v>
       </c>
       <c r="Q3">
-        <v>21.67250194521048</v>
+        <v>21.67250194521047</v>
       </c>
       <c r="R3">
         <v>-99.65273561736714</v>
@@ -9035,55 +9035,55 @@
         <v>1.210751047633806</v>
       </c>
       <c r="D4">
-        <v>0.9664867210300013</v>
+        <v>0.9664867210300018</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>13.98054886545998</v>
+        <v>13.98054886545999</v>
       </c>
       <c r="G4">
-        <v>11.1600273710974</v>
+        <v>11.16002737109741</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9044874322036915</v>
+        <v>0.9044874322036917</v>
       </c>
       <c r="O4">
         <v>0.7019303077933687</v>
       </c>
       <c r="P4">
-        <v>0.8518384756869165</v>
+        <v>0.8518384756869166</v>
       </c>
       <c r="Q4">
-        <v>19.80759473074443</v>
+        <v>19.80759473074442</v>
       </c>
       <c r="R4">
-        <v>-97.63434507042334</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
         <v>152.8122609529874</v>
       </c>
       <c r="T4">
-        <v>0.9264880498917321</v>
+        <v>0.9264880498917325</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O5">
-        <v>0.7345230598571354</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P5">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092762</v>
       </c>
       <c r="Q5">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290828</v>
       </c>
       <c r="R5">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S5">
-        <v>-2.943389200552513</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O6">
-        <v>0.7345230598571354</v>
+        <v>0.701930307757029</v>
       </c>
       <c r="P6">
-        <v>0.9300083243828786</v>
+        <v>0.8518384757092762</v>
       </c>
       <c r="Q6">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R6">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S6">
-        <v>-2.943389200552517</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9385,16 +9385,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209809371</v>
+        <v>0.9677452209809372</v>
       </c>
       <c r="O3">
-        <v>0.8139299031202699</v>
+        <v>0.8139299031202697</v>
       </c>
       <c r="P3">
-        <v>0.883172455503468</v>
+        <v>0.8831724555034682</v>
       </c>
       <c r="Q3">
-        <v>21.67250194521048</v>
+        <v>21.67250194521047</v>
       </c>
       <c r="R3">
         <v>-99.65273561736714</v>
@@ -9417,55 +9417,55 @@
         <v>1.210751047633806</v>
       </c>
       <c r="D4">
-        <v>0.9664867210300013</v>
+        <v>0.9664867210300018</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>13.98054886545998</v>
+        <v>13.98054886545999</v>
       </c>
       <c r="G4">
-        <v>11.1600273710974</v>
+        <v>11.16002737109741</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512645</v>
       </c>
       <c r="I4">
-        <v>1.940063662238626</v>
+        <v>1.940063662238619</v>
       </c>
       <c r="J4">
-        <v>1.113751880253972</v>
+        <v>1.113751880253971</v>
       </c>
       <c r="K4">
-        <v>3.006397543748692</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
         <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543745535</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9044874322036915</v>
+        <v>0.9044874322036917</v>
       </c>
       <c r="O4">
         <v>0.7019303077933687</v>
       </c>
       <c r="P4">
-        <v>0.8518384756869165</v>
+        <v>0.8518384756869166</v>
       </c>
       <c r="Q4">
-        <v>19.80759473074443</v>
+        <v>19.80759473074442</v>
       </c>
       <c r="R4">
-        <v>-97.63434507042334</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
         <v>152.8122609529874</v>
       </c>
       <c r="T4">
-        <v>0.9264880498917321</v>
+        <v>0.9264880498917325</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O5">
-        <v>0.7345230598571354</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P5">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092762</v>
       </c>
       <c r="Q5">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290828</v>
       </c>
       <c r="R5">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S5">
-        <v>-2.943389200552513</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O6">
-        <v>0.7345230598571354</v>
+        <v>0.701930307757029</v>
       </c>
       <c r="P6">
-        <v>0.9300083243828786</v>
+        <v>0.8518384757092762</v>
       </c>
       <c r="Q6">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R6">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S6">
-        <v>-2.943389200552517</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9645,7 +9645,7 @@
         <v>1.056966443490338</v>
       </c>
       <c r="G2">
-        <v>-1.342925561278417</v>
+        <v>-1.342925561278413</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.891057042038613</v>
+        <v>0.8910570420386137</v>
       </c>
       <c r="G3">
-        <v>-9.168679204911165</v>
+        <v>-9.16867920491114</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9682,16 +9682,16 @@
         <v>45.36885473474868</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354138</v>
+        <v>0.6277319163354118</v>
       </c>
       <c r="E4">
-        <v>2.898438697960061</v>
+        <v>2.898438697960063</v>
       </c>
       <c r="F4">
-        <v>0.8020156209364409</v>
+        <v>0.8020156209364414</v>
       </c>
       <c r="G4">
-        <v>45.00000000014392</v>
+        <v>45.00000000014397</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8020156208827656</v>
+        <v>0.802015620882755</v>
       </c>
       <c r="G5">
-        <v>-159.5296738926599</v>
+        <v>-9.529673892666253</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8020156208827656</v>
+        <v>0.802015620882755</v>
       </c>
       <c r="G6">
-        <v>-159.5296738926599</v>
+        <v>-9.529673892666253</v>
       </c>
     </row>
   </sheetData>
@@ -9790,10 +9790,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8500049525313292</v>
+        <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408795</v>
+        <v>-2.653816313408782</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.361720183501133</v>
+        <v>0.3617201835011319</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526819</v>
+        <v>-39.09154322526811</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9824,22 +9824,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.601610081969428</v>
+        <v>3.601610081969432</v>
       </c>
       <c r="C4">
-        <v>124.7634330204671</v>
+        <v>124.7634330204673</v>
       </c>
       <c r="D4">
-        <v>1.113751880252863</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.006397543745613</v>
+        <v>3.00639754374561</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.67231643316975</v>
+        <v>69.6723164331698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9938,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8500049525313292</v>
+        <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408795</v>
+        <v>-2.653816313408782</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9961,10 +9961,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.361720183501133</v>
+        <v>0.3617201835011319</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526819</v>
+        <v>-39.09154322526811</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9972,22 +9972,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.601610081969428</v>
+        <v>3.601610081969432</v>
       </c>
       <c r="C4">
-        <v>124.7634330204671</v>
+        <v>124.7634330204673</v>
       </c>
       <c r="D4">
-        <v>1.113751880252863</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.006397543745613</v>
+        <v>3.00639754374561</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.67231643316975</v>
+        <v>69.6723164331698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10089,7 +10089,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992046</v>
+        <v>-1.557899718992042</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8139299031165274</v>
+        <v>0.8139299031165275</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430418</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10123,19 +10123,19 @@
         <v>1.146247392719871</v>
       </c>
       <c r="C4">
-        <v>39.70717444468344</v>
+        <v>39.70717444468345</v>
       </c>
       <c r="D4">
-        <v>1.113751880252863</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.006397543745613</v>
+        <v>3.00639754374561</v>
       </c>
       <c r="F4">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986812</v>
+        <v>44.99999999986815</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532707</v>
+        <v>0.7019303077532579</v>
       </c>
       <c r="G5">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849613</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532707</v>
+        <v>0.7019303077532579</v>
       </c>
       <c r="G6">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849613</v>
       </c>
     </row>
   </sheetData>
@@ -10237,7 +10237,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992046</v>
+        <v>-1.557899718992042</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8139299031165274</v>
+        <v>0.8139299031165275</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430418</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10271,19 +10271,19 @@
         <v>1.146247392719871</v>
       </c>
       <c r="C4">
-        <v>39.70717444468344</v>
+        <v>39.70717444468345</v>
       </c>
       <c r="D4">
-        <v>1.113751880252863</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.006397543745613</v>
+        <v>3.00639754374561</v>
       </c>
       <c r="F4">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986812</v>
+        <v>44.99999999986815</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532707</v>
+        <v>0.7019303077532579</v>
       </c>
       <c r="G5">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849613</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532707</v>
+        <v>0.7019303077532579</v>
       </c>
       <c r="G6">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849613</v>
       </c>
     </row>
   </sheetData>
@@ -10454,7 +10454,7 @@
         <v>25.98965116739708</v>
       </c>
       <c r="R2">
-        <v>-91.13019952201601</v>
+        <v>-91.130199522016</v>
       </c>
       <c r="S2">
         <v>153.5693903185486</v>
@@ -10507,13 +10507,13 @@
         <v>0.291705603751294</v>
       </c>
       <c r="P3">
-        <v>0.8906876332644386</v>
+        <v>0.8906876332644384</v>
       </c>
       <c r="Q3">
-        <v>7.091324389062541</v>
+        <v>7.091324389062547</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550799</v>
+        <v>-119.1713773550798</v>
       </c>
       <c r="S3">
         <v>171.7794727726615</v>
@@ -10527,49 +10527,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.70915442393707</v>
+        <v>3.709154423937069</v>
       </c>
       <c r="D4">
-        <v>3.70915442393707</v>
+        <v>3.709154423937069</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.82962610251918</v>
+        <v>42.82962610251916</v>
       </c>
       <c r="G4">
-        <v>42.82962610251918</v>
+        <v>42.82962610251916</v>
       </c>
       <c r="H4">
-        <v>3.698069333823729</v>
+        <v>3.69806933382373</v>
       </c>
       <c r="I4">
-        <v>1.935851081753641</v>
+        <v>1.935851081753642</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162203</v>
+        <v>0.6277319163162204</v>
       </c>
       <c r="K4">
         <v>2.898438697979806</v>
       </c>
       <c r="L4">
-        <v>0.627731916363975</v>
+        <v>0.6277319163639747</v>
       </c>
       <c r="M4">
         <v>2.898438697959988</v>
       </c>
       <c r="N4">
-        <v>0.9526279648032092</v>
+        <v>0.9526279648032087</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648047559</v>
+        <v>0.9526279648047558</v>
       </c>
       <c r="Q4">
-        <v>-1.251027744853947E-11</v>
+        <v>-1.250855737550043E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000115981061</v>
+        <v>0.9526279646198192</v>
       </c>
       <c r="O5">
-        <v>0.5500000122361737</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.10000002383428</v>
+        <v>0.9526279649881451</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999967092</v>
+        <v>1.096042576561009E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999967107</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.378563411667719E-13</v>
+        <v>179.9999999988957</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000115981062</v>
+        <v>0.9526279646198192</v>
       </c>
       <c r="O6">
-        <v>0.5500000122361736</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.10000002383428</v>
+        <v>0.9526279649881453</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999967092</v>
+        <v>1.096039847146626E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999967107</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.345176246909041E-13</v>
+        <v>179.9999999988957</v>
       </c>
     </row>
   </sheetData>
